--- a/survey_templates/034_online_knowledge_sharing_behavior_survey--survey_templates.xlsx
+++ b/survey_templates/034_online_knowledge_sharing_behavior_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'7-1',_'name':_'page_2_question_1_option_1',_'label':_'curiosity',_'hint':_none}</t>
+          <t>curiosity</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': '7-1', 'name': 'page_2_question_1_option_1', 'label': 'Curiosity', 'hint': None}</t>
+          <t>Curiosity</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'7-2',_'name':_'page_2_question_1_option_2',_'label':_'to_help_others',_'hint':_none}</t>
+          <t>to_help_others</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': '7-2', 'name': 'page_2_question_1_option_2', 'label': 'To help others', 'hint': None}</t>
+          <t>To help others</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'7-3',_'name':_'page_2_question_1_option_3',_'label':_'for_personal_gain',_'hint':_none}</t>
+          <t>for_personal_gain</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': '7-3', 'name': 'page_2_question_1_option_3', 'label': 'For personal gain', 'hint': None}</t>
+          <t>For personal gain</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'9-1',_'name':_'page_3_question_1_option_1',_'label':_'researcher',_'hint':_none}</t>
+          <t>researcher</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': '9-1', 'name': 'page_3_question_1_option_1', 'label': 'Researcher', 'hint': None}</t>
+          <t>Researcher</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'9-2',_'name':_'page_3_question_1_option_2',_'label':_'hr',_'hint':_none}</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': '9-2', 'name': 'page_3_question_1_option_2', 'label': 'HR', 'hint': None}</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'9-3',_'name':_'page_3_question_1_option_3',_'label':_'educator',_'hint':_none}</t>
+          <t>educator</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': '9-3', 'name': 'page_3_question_1_option_3', 'label': 'Educator', 'hint': None}</t>
+          <t>Educator</t>
         </is>
       </c>
     </row>
